--- a/workaw_data.xlsx
+++ b/workaw_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kuck\Documents\AI\demo\workaw_chatbot\workaw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213A20B0-28C2-4AFD-A81D-AA7E68059140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909B913C-0A6C-47A3-A2DC-EFB8F1CBA00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13996" xr2:uid="{64D59F0A-8640-4EF3-95CC-009CBE3BA196}"/>
   </bookViews>
@@ -39,169 +39,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>context</t>
-  </si>
-  <si>
-    <t>หลักสูตรครุศาสตรบัณฑิต สาขาวิชานวัตกรรมการจัดการเรียนรู้
-(หลักสูตรปรับปรุง พ.ศ. 2567)
-ชื่อสถาบันอุดมศึกษา มหาวิทยาลัยกาฬสินธุ์
-คณะ คณะศึกษาศาสตร์และนวัตกรรมการศึกษา
-ชื่อหลักสูตร
-หลักสูตรครุศาสตรบัณฑิต สาขาวิชานวัตกรรมการจัดการเรียนรู้ (4 ปี)
-Bachelor of Education Program in Learning Management Innovation
-ชื่อปริญญาและสาขาวิชา
-ชื่อเต็มภาษาไทย ครุศาสตรบัณฑิต (นวัตกรรมการจัดการเรียนรู้)
-ชื่อย่อภาษาไทย ค.บ. (นวัตกรรมการจัดการเรียนรู้)
-ชื่อเต็มภาษาอังกฤษ Bachelor of Education (Learning Management Innovation)
-ชื่อย่อภาษาอังกฤษ B.Ed. (Learning Management Innovation)
-วิชาเอก ประกอบด้วย
-1. วิทยาศาสตร์ทั่วไป
-2. คณิตศาสตร์
-3. คอมพิวเตอร์
-4. การศึกษาปฐมวัย
-5. ภาษาไทย
-6. ภาษาอังกฤษ
-7. สังคมศึกษา
-8. ฟิสิกส์
-9. ชีววิทยา
-10. พลศึกษา
-11. การประถมศึกษา
-12. เกษตรศาสตร์
-หมายเหตุนักศึกษาสามารถเลือกเรียนได้ทั้งรูปแบบเอกเดี่ยวหรือเอกคู่ หากเลือกแบบเอกคู่สามารถเลือก
-วิชาเอก ที่ 2 ได้ทุกวิชาเอกในหลักสูตร
-อาชีพที่สามารถประกอบได้หลังสำเร็จการศึกษา
-1. ครูและบุคลากรทางการศึกษา 
-2. นวัตกรการจัดการเรียนรู้ 
-3. โค้ช พี่เลี้ยง กระบวนกร นักจัดกิจกรรม 
-4. ผู้ประกอบการด้านการจัดการเรียนรู้ 
-5. นักออกแบบผลิตภัณฑ์ทางการเรียนรู้
-จำนวนหน่วยกิตที่เรียนตลอดหลักสูตร
-- วิชาเอกเดี่ยว รวมตลอดหลักสูตร กำหนดให้เรียน 140 หน่วยกิต
-- วิชาเอกคู่ รวมตลอดหลักสูตร กำหนดให้เรียน 182 หน่วยกิต
-โครงสร้างหลักสูตร
-รูปแบบเอกเดี่ยว จำนวนหน่วยกิตรวมตลอดหลักสูตร ไม่น้อยกว่า 140 หน่วยกิต
-1. หมวดวิชาศึกษาทั่วไป ไม่น้อยกว่า 24 หน่วยกิต
-1.1 กลุ่มวิชาบังคับ 18 หน่วยกิต
-1.2 กลุ่มวิชาเลือก 6 หน่วยกิต
-2. หมวดวิชาเฉพาะ ไม่น้อยกว่า 110 หน่วยกิต
-2.1 ชุดวิชาชีพครู 41 หน่วยกิต
-2.1.1 กลุ่มวิชาชีพครูบังคับ 36 หน่วยกิต
-2.1.2 กลุ่มวิชาชีพครูเลือก 5 หน่วยกิต
-2.2 ชุดวิชาเอก 57 หน่วยกิต
-2.2.1 กลุ่มวิชาเอกบังคับ 42 หน่วยกิต
-2.2.2 กลุ่มวิชาเอกเลือก 15 หน่วยกิต
-2.3 ชุดวิชามาตรฐานประสบการณ์วิชาชีพ 12 หน่วยกิต
-2.3.1 การฝึกประสบการณ์วิชาชีพระหว่างเรียน 6 หน่วยกิต
-2.3.2 การปฏิบัติการสอนในสถานศึกษา 6 หน่วยกิต
-3. หมวดวิชาเลือกเสรี ไม่น้อยกว่า 6 หน่วยกิต
-รวม 140 หน่วยกิต
-รูปแบบเอกคู่ จำนวนหน่วยกิตรวมตลอดหลักสูตร ไม่น้อยกว่า 182 หน่วยกิต
-1. หมวดวิชาศึกษาทั่วไป ไม่น้อยกว่า 24 หน่วยกิต
-1.1 กลุ่มวิชาบังคับ 18 หน่วยกิต
-1.2 กลุ่มวิชาเลือก 6 หน่วยกิต
-2. หมวดวิชาเฉพาะ ไม่น้อยกว่า 152 หน่วยกิต
-2.1 ชุดวิชาชีพครู 41 หน่วยกิต
-2.1.1 กลุ่มวิชาชีพครูบังคับ 36 หน่วยกิต
-2.1.2 กลุ่มวิชาชีพเลือก 5 หน่วยกิต
-2.2 ชุดวิชาเอก 57 หน่วยกิต
-2.2.1 กลุ่มวิชาเอกบังคับ 42 หน่วยกิต
-2.2.2 กลุ่มวิชาเอกเลือก 15 หน่วยกิต
-2.3 ชุดวิชาเอกที่สอง 42 หน่วยกิต
-2.4 ชุดวิชามาตรฐานประสบการณ์วิชาชีพ 12 หน่วยกิต
-2.4.1 การฝึกประสบการณ์วิชาชีพระหว่างเรียน 6 หน่วยกิต
-2.4.2 การปฏิบัติการสอนในสถานศึกษา 6 หน่วยกิต
-3. หมวดวิชาเลือกเสรี ไม่น้อยกว่า 6 หน่วยกิต
-รวม 182 หน่วยกิต
-คุณสมบัติของผู้เข้าศึกษา
-1.สำเร็จการศึกษาระดับมัธยมศึกษาตอนปลาย หรือเทียบเท่า
-อัตราค่าธรรมเนียมการศึกษา
-8,500 บาท/เทอม
-การรับสมัครนักศึกษา ปีการศึกษา 2569 หลักสูตรครุศาสตรบัณฑิต สาขาวิชานวัตกรรมการจัดการเรียนรู้ (4 ปี)
-1. รอบ 1 Portfolio
-2. รอบ 2 Quota
-3. รอบ 4 Direct Admission
-เปิดรับสมัคร จำนวน 3 รอบ
-รอบ 1 Portfolio
-รายละเอียดเกณฑ์การคัดเลือก
-1. เป็นผู้ที่กำลังศึกษาอยู่ชั้นมัธยมศึกษาปีที่ 6 หรือ ปวช. หรือเทียบเท่า หรือเป็นผู้สำเร็จการศึกษาชั้นมัธยมศึกษาปีที่ 6 หรือ ปวช. หรือเทียบเท่า
-2. ต้องมีผลการเรียนเฉลี่ยสะสม (GPAX) ขั้นต่ำ 4 ภาคเรียน 2.50 ขึ้นไป
-3. วัดแววความเป็นครู
-สมัครผ่านระบบออนไลน์ 
-https://admission.ksu.ac.th/ พร้อมชำระค่าสมัคร 200 บาท
-แผนรับเข้าศึกษา จำนวน(คน)
-1. วิทยาศาสตร์ทั่วไป 40 คน
-2. คณิตศาสตร์ 30 คน
-3. คอมพิวเตอร์ 15 คน
-4. การศึกษาปฐมวัย 30 คน
-5. ภาษาไทย 35 คน
-6. ภาษาอังกฤษ 15 คน
-7. สังคมศึกษา 10 คน
-8. ฟิสิกส์ 15 คน
-9. ชีววิทยา 15 คน
-10. พลศึกษา 20 คน
-11. การประถมศึกษา 25 คน
-12. เกษตรศาสตร์ 15 คน
-กำหนดปฏิทินรับสมัครนักศึกษา รอบ 1 Portfolio
--สมัครผ่านระบบออนไลน์ วันที่ 29 กรกฎาคม 2568 ถึง วันที่ 3 พฤศจิกายน 2568
--ประกาศรายชื่อผู้มีสิทธิ์สอบคัดเลือก วันที่ 6 พฤศจิกายน 2568
--สอบคัดเลือก / สอบสัมภาษณ์ วันที่ 8 พฤศจิกายน 2568
--ประกาศรายชื่อผู้ผ่านการคัดเลือกและมีสิทธิ์เข้าศึกษา วันที่ 12 พฤศจิกายน 2568
--รายงานตัวขึ้นทะเบียนเป็นนักศึกษาและชำระเงิน ผ่านระบบบริการการศึกษา ESS วันที่ 13 - 28 พฤศจิกายน 2568
--ยืนยันสิทธิ์ในระบบ TCAS วันที่ 6 - 7 กุมภาพันธ์ 2569
-รอบ 2 Quota
-รายละเอียดเกณฑ์การคัดเลือก
-1. เป็นผู้ที่กำลังศึกษาอยู่ชั้นมัธยมศึกษาปีที่ 6 หรือ ปวช. หรือเทียบเท่า หรือเป็นผู้สำเร็จการศึกษาชั้นมัธยมศึกษาปีที่ 6 หรือ ปวช. หรือเทียบเท่า
-2. ต้องมีผลการเรียนเฉลี่ยสะสม (GPAX) ขั้นต่ำ 4 ภาคเรียน 2.50 ขึ้นไป
-3. ต้องมีผลคะแนน TPAT5
-4. วัดแววความเป็นครู
-สมัครผ่านระบบออนไลน์
- https://admission.ksu.ac.th/ พร้อมชำระค่าสมัคร 200 บาท
-แผนรับเข้าศึกษา จำนวน(คน)
-1. วิทยาศาสตร์ทั่วไป 15 คน
-2. คณิตศาสตร์ 20 คน
-3. คอมพิวเตอร์ 10 คน
-4. การศึกษาปฐมวัย 20 คน
-5. ภาษาไทย 20 คน
-6. ภาษาอังกฤษ 10 คน
-7. สังคมศึกษา 10 คน
-8. ฟิสิกส์ 10 คน
-9. ชีววิทยา 10 คน
-10. พลศึกษา 10 คน
-11. การประถมศึกษา 25 คน
-12. เกษตรศาสตร์ 10 คน
-กำหนดปฏิทินรับสมัครนักศึกษา รอบ 2 Quota
--สมัครผ่านระบบออนไลน์ วันที่ 2 ธันวาคม 2568 ถึง วันที่ 4 มกราคม 2569
--ประกาศรายชื่อผู้มีสิทธิ์สอบคัดเลือก วันที่ 7 มกราคม 2569
--สอบคัดเลือก / สอบสัมภาษณ์ วันที่ 10 มกราคม 2569
--ประกาศรายชื่อผู้ผ่านการคัดเลือกและมีสิทธิ์เข้าศึกษา วันที่ 14 มกราคม 2569
--รายงานตัวขึ้นทะเบียนเป็นนักศึกษาและชำระเงิน ผ่านระบบบริการการศึกษา ESS วันที่ 15 - 31 มกราคม 2569
--ยืนยันสิทธิ์ในระบบ TCAS วันที่ 2 - 3 พฤษภาคม 2569
-รอบ 3 Direct Admission
-รายละเอียดเกณฑ์การคัดเลือก
-1. เป็นผู้ที่กำลังศึกษาอยู่ชั้นมัธยมศึกษาปีที่ 6 หรือ ปวช. หรือเทียบเท่า หรือเป็นผู้สำเร็จการศึกษาชั้นมัธยมศึกษาปีที่ 6 หรือ ปวช. หรือเทียบเท่า
-2. ต้องมีผลการเรียนเฉลี่ยสะสม (GPAX) ขั้นต่ำ 4 ภาคเรียน 2.50 ขึ้นไป
-สมัครผ่านระบบออนไลน์ 
-https://admission.ksu.ac.th/ พร้อมชำระค่าสมัคร 200 บาท
-แผนรับเข้าศึกษา จำนวน(คน)
-1. วิทยาศาสตร์ทั่วไป 5 คน
-2. คณิตศาสตร์ 10 คน
-3. คอมพิวเตอร์ 5 คน
-4. การศึกษาปฐมวัย 10 คน
-5. ภาษาไทย 5 คน
-6. ภาษาอังกฤษ 5 คน
-7. สังคมศึกษา 10 คน
-8. ฟิสิกส์ 5 คน
-9. ชีววิทยา 5 คน
-10. พลศึกษา 0 คน
-11. การประถมศึกษา 10 คน
-12. เกษตรศาสตร์ 5 คน
-กำหนดปฏิทินรับสมัครนักศึกษา รอบ 3 Direct Admission
--สมัครผ่านระบบออนไลน์ วันที่ 22 พฤษภาคม 2569 ถึง วันที่ 11 มิถุนายน 2569
--ประกาศรายชื่อผู้มีสิทธิ์สอบคัดเลือก วันที่ 12 มิถุนายน 2569
--สอบคัดเลือก / สอบสัมภาษณ์ วันที่ 13 มิถุนายน 2569
--ประกาศรายชื่อผู้ผ่านการคัดเลือกและมีสิทธิ์เข้าศึกษา วันที่ 16 มิถุนายน 2569
--รายงานตัวขึ้นทะเบียนเป็นนักศึกษาและชำระเงิน ผ่านระบบบริการการศึกษา ESS วันที่ 17 - 20 มิถุนายน 2569
-วันเปิดภาคเรียน 
-วันที่ 22 มิถุนายน 2569</t>
   </si>
   <si>
     <t>หลักสูตรประกาศนียบัตรบัณฑิต สาขาวิชานวัตกรรมการจัดการเรียนรู้
@@ -781,6 +618,167 @@
 14.นางสาวศุภลักษณา ภูกาสอน (ตำแหน่งเจ้าหน้าที่บริหารงานทั่วไป รับผิดชอบงานบริหารและวางแผน)
 15.นางสาวนาฎนภา นามเขต (ตำแหน่งนักวิชาการศึกษา รับผิดชอบงานโครงการครูรัก(ษ์)ถิ่น)</t>
   </si>
+  <si>
+    <t>หลักสูตรครุศาสตรบัณฑิต สาขาวิชานวัตกรรมการจัดการเรียนรู้
+(หลักสูตรปรับปรุง พ.ศ. 2567)
+ชื่อสถาบันอุดมศึกษา มหาวิทยาลัยกาฬสินธุ์
+คณะ คณะศึกษาศาสตร์และนวัตกรรมการศึกษา
+ชื่อหลักสูตร
+หลักสูตรครุศาสตรบัณฑิต สาขาวิชานวัตกรรมการจัดการเรียนรู้ (4 ปี)
+Bachelor of Education Program in Learning Management Innovation
+ชื่อปริญญาและสาขาวิชา
+ชื่อเต็มภาษาไทย ครุศาสตรบัณฑิต (นวัตกรรมการจัดการเรียนรู้)
+ชื่อย่อภาษาไทย ค.บ. (นวัตกรรมการจัดการเรียนรู้)
+ชื่อเต็มภาษาอังกฤษ Bachelor of Education (Learning Management Innovation)
+ชื่อย่อภาษาอังกฤษ B.Ed. (Learning Management Innovation)
+วิชาเอก ประกอบด้วย
+1. วิทยาศาสตร์ทั่วไป
+2. คณิตศาสตร์
+3. คอมพิวเตอร์
+4. การศึกษาปฐมวัย
+5. ภาษาไทย
+6. ภาษาอังกฤษ
+7. สังคมศึกษา
+8. ฟิสิกส์
+9. ชีววิทยา
+10. พลศึกษา
+11. การประถมศึกษา
+12. เกษตรศาสตร์
+หมายเหตุนักศึกษาสามารถเลือกเรียนได้ทั้งรูปแบบเอกเดี่ยวหรือเอกคู่ หากเลือกแบบเอกคู่สามารถเลือก
+วิชาเอก ที่ 2 ได้ทุกวิชาเอกในหลักสูตร
+อาชีพที่สามารถประกอบได้หลังสำเร็จการศึกษา
+1. ครูและบุคลากรทางการศึกษา 
+2. นวัตกรการจัดการเรียนรู้ 
+3. โค้ช พี่เลี้ยง กระบวนกร นักจัดกิจกรรม 
+4. ผู้ประกอบการด้านการจัดการเรียนรู้ 
+5. นักออกแบบผลิตภัณฑ์ทางการเรียนรู้
+จำนวนหน่วยกิตที่เรียนตลอดหลักสูตร
+- วิชาเอกเดี่ยว รวมตลอดหลักสูตร กำหนดให้เรียน 140 หน่วยกิต
+- วิชาเอกคู่ รวมตลอดหลักสูตร กำหนดให้เรียน 182 หน่วยกิต
+โครงสร้างหลักสูตร
+รูปแบบเอกเดี่ยว จำนวนหน่วยกิตรวมตลอดหลักสูตร ไม่น้อยกว่า 140 หน่วยกิต
+1. หมวดวิชาศึกษาทั่วไป ไม่น้อยกว่า 24 หน่วยกิต
+1.1 กลุ่มวิชาบังคับ 18 หน่วยกิต
+1.2 กลุ่มวิชาเลือก 6 หน่วยกิต
+2. หมวดวิชาเฉพาะ ไม่น้อยกว่า 110 หน่วยกิต
+2.1 ชุดวิชาชีพครู 41 หน่วยกิต
+2.1.1 กลุ่มวิชาชีพครูบังคับ 36 หน่วยกิต
+2.1.2 กลุ่มวิชาชีพครูเลือก 5 หน่วยกิต
+2.2 ชุดวิชาเอก 57 หน่วยกิต
+2.2.1 กลุ่มวิชาเอกบังคับ 42 หน่วยกิต
+2.2.2 กลุ่มวิชาเอกเลือก 15 หน่วยกิต
+2.3 ชุดวิชามาตรฐานประสบการณ์วิชาชีพ 12 หน่วยกิต
+2.3.1 การฝึกประสบการณ์วิชาชีพระหว่างเรียน 6 หน่วยกิต
+2.3.2 การปฏิบัติการสอนในสถานศึกษา 6 หน่วยกิต
+3. หมวดวิชาเลือกเสรี ไม่น้อยกว่า 6 หน่วยกิต
+รวม 140 หน่วยกิต
+รูปแบบเอกคู่ จำนวนหน่วยกิตรวมตลอดหลักสูตร ไม่น้อยกว่า 182 หน่วยกิต
+1. หมวดวิชาศึกษาทั่วไป ไม่น้อยกว่า 24 หน่วยกิต
+1.1 กลุ่มวิชาบังคับ 18 หน่วยกิต
+1.2 กลุ่มวิชาเลือก 6 หน่วยกิต
+2. หมวดวิชาเฉพาะ ไม่น้อยกว่า 152 หน่วยกิต
+2.1 ชุดวิชาชีพครู 41 หน่วยกิต
+2.1.1 กลุ่มวิชาชีพครูบังคับ 36 หน่วยกิต
+2.1.2 กลุ่มวิชาชีพเลือก 5 หน่วยกิต
+2.2 ชุดวิชาเอก 57 หน่วยกิต
+2.2.1 กลุ่มวิชาเอกบังคับ 42 หน่วยกิต
+2.2.2 กลุ่มวิชาเอกเลือก 15 หน่วยกิต
+2.3 ชุดวิชาเอกที่สอง 42 หน่วยกิต
+2.4 ชุดวิชามาตรฐานประสบการณ์วิชาชีพ 12 หน่วยกิต
+2.4.1 การฝึกประสบการณ์วิชาชีพระหว่างเรียน 6 หน่วยกิต
+2.4.2 การปฏิบัติการสอนในสถานศึกษา 6 หน่วยกิต
+3. หมวดวิชาเลือกเสรี ไม่น้อยกว่า 6 หน่วยกิต
+รวม 182 หน่วยกิต
+คุณสมบัติของผู้เข้าศึกษา
+1.สำเร็จการศึกษาระดับมัธยมศึกษาตอนปลาย หรือเทียบเท่า
+อัตราค่าธรรมเนียมการศึกษา
+8,500 บาท/เทอม
+การรับสมัครนักศึกษา ปีการศึกษา 2569 หลักสูตรครุศาสตรบัณฑิต สาขาวิชานวัตกรรมการจัดการเรียนรู้ (4 ปี)
+1. รอบ 1 Portfolio
+2. รอบ 2 Quota
+3. รอบ 4 Direct Admission
+เปิดรับสมัคร จำนวน 3 รอบ
+รอบ 1 Portfolio
+รายละเอียดเกณฑ์การคัดเลือก
+1. เป็นผู้ที่กำลังศึกษาอยู่ชั้นมัธยมศึกษาปีที่ 6 หรือ ปวช. หรือเทียบเท่า หรือเป็นผู้สำเร็จการศึกษาชั้นมัธยมศึกษาปีที่ 6 หรือ ปวช. หรือเทียบเท่า
+2. ต้องมีผลการเรียนเฉลี่ยสะสม (GPAX) ขั้นต่ำ 4 ภาคเรียน 2.50 ขึ้นไป
+3. วัดแววความเป็นครู
+สมัครผ่านระบบออนไลน์ 
+https://admission.ksu.ac.th/ พร้อมชำระค่าสมัคร 200 บาท
+แผนรับเข้าศึกษา จำนวน(คน)
+1. วิทยาศาสตร์ทั่วไป 40 คน
+2. คณิตศาสตร์ 30 คน
+3. คอมพิวเตอร์ 15 คน
+4. การศึกษาปฐมวัย 30 คน
+5. ภาษาไทย 35 คน
+6. ภาษาอังกฤษ 15 คน
+7. สังคมศึกษา 10 คน
+8. ฟิสิกส์ 15 คน
+9. ชีววิทยา 15 คน
+10. พลศึกษา 20 คน
+11. การประถมศึกษา 25 คน
+12. เกษตรศาสตร์ 15 คน
+กำหนดปฏิทินรับสมัครนักศึกษา รอบ 1 Portfolio
+-สมัครผ่านระบบออนไลน์ วันที่ 29 กรกฎาคม 2568 ถึง วันที่ 3 พฤศจิกายน 2568
+-ประกาศรายชื่อผู้มีสิทธิ์สอบคัดเลือก วันที่ 6 พฤศจิกายน 2568
+-สอบคัดเลือก / สอบสัมภาษณ์ วันที่ 8 พฤศจิกายน 2568
+-ประกาศรายชื่อผู้ผ่านการคัดเลือกและมีสิทธิ์เข้าศึกษา วันที่ 12 พฤศจิกายน 2568
+-รายงานตัวขึ้นทะเบียนเป็นนักศึกษาและชำระเงิน ผ่านระบบบริการการศึกษา ESS วันที่ 13 - 28 พฤศจิกายน 2568
+-ยืนยันสิทธิ์ในระบบ TCAS วันที่ 6 - 7 กุมภาพันธ์ 2569
+รอบ 2 Quota
+รายละเอียดเกณฑ์การคัดเลือก
+1. เป็นผู้ที่กำลังศึกษาอยู่ชั้นมัธยมศึกษาปีที่ 6 หรือ ปวช. หรือเทียบเท่า หรือเป็นผู้สำเร็จการศึกษาชั้นมัธยมศึกษาปีที่ 6 หรือ ปวช. หรือเทียบเท่า
+2. ต้องมีผลการเรียนเฉลี่ยสะสม (GPAX) ขั้นต่ำ 4 ภาคเรียน 2.50 ขึ้นไป
+3. ต้องมีผลคะแนน TPAT5
+4. วัดแววความเป็นครู
+สมัครผ่านระบบออนไลน์
+ https://admission.ksu.ac.th/ พร้อมชำระค่าสมัคร 200 บาท
+แผนรับเข้าศึกษา จำนวน(คน)
+1. วิทยาศาสตร์ทั่วไป 15 คน
+2. คณิตศาสตร์ 20 คน
+3. คอมพิวเตอร์ 10 คน
+4. การศึกษาปฐมวัย 20 คน
+5. ภาษาไทย 20 คน
+6. ภาษาอังกฤษ 10 คน
+7. สังคมศึกษา 10 คน
+8. ฟิสิกส์ 10 คน
+9. ชีววิทยา 10 คน
+10. พลศึกษา 10 คน
+11. การประถมศึกษา 25 คน
+12. เกษตรศาสตร์ 10 คน
+กำหนดปฏิทินรับสมัครนักศึกษา รอบ 2 Quota
+-สมัครผ่านระบบออนไลน์ วันที่ 2 ธันวาคม 2568 ถึง วันที่ 4 มกราคม 2569
+-ประกาศรายชื่อผู้มีสิทธิ์สอบคัดเลือก วันที่ 7 มกราคม 2569
+-สอบคัดเลือก / สอบสัมภาษณ์ วันที่ 10 มกราคม 2569
+-ประกาศรายชื่อผู้ผ่านการคัดเลือกและมีสิทธิ์เข้าศึกษา วันที่ 14 มกราคม 2569
+-รายงานตัวขึ้นทะเบียนเป็นนักศึกษาและชำระเงิน ผ่านระบบบริการการศึกษา ESS วันที่ 15 - 31 มกราคม 2569
+-ยืนยันสิทธิ์ในระบบ TCAS วันที่ 2 - 3 พฤษภาคม 2569
+รอบ 2 Quota ครั้งที่ 3
+รายละเอียดเกณฑ์การคัดเลือก
+1. เป็นผู้ที่กำลังศึกษาอยู่ชั้นมัธยมศึกษาปีที่ 6 หรือ ปวช. หรือเทียบเท่า หรือเป็นผู้สำเร็จการศึกษาชั้นมัธยมศึกษาปีที่ 6 หรือ ปวช. หรือเทียบเท่า
+2. ต้องมีผลการเรียนเฉลี่ยสะสม (GPAX) ขั้นต่ำ 4 ภาคเรียน 2.50 ขึ้นไป
+3. ต้องมีผลคะแนน TPAT5 (ถ้ามี)
+4. วัดแววความเป็นครู
+สมัครผ่านระบบออนไลน์
+ https://admission.ksu.ac.th/ พร้อมชำระค่าสมัคร 200 บาท
+แผนรับเข้าศึกษา จำนวน 6 วิชาเอก
+1. วิทยาศาสตร์ทั่วไป รับจำนวน 15 คน
+2. คอมพิวเตอร์ รับจำนวน 15 คน
+3. ภาษาอังกฤษ รับจำนวน 15 คน
+4. ฟิสิกส์ รับจำนวน 15 คน
+5. ชีววิทยา รับจำนวน 15 คน
+6. เกษตรศาสตร์ รับจำนวน 15 คน
+กำหนดปฏิทินรับสมัครนักศึกษา รอบ 2 Quota ครั้งที่ 3
+-สมัครผ่านระบบออนไลน์ วันที่ 2 เมษายน 2569 ถึง วันที่ 20 เมษายน 2569
+-ประกาศรายชื่อผู้มีสิทธิ์สอบคัดเลือก วันที่ 23 เมษายน 2569
+-สอบคัดเลือก / สอบสัมภาษณ์ วันที่ 25 เมษายน 2569
+-ประกาศรายชื่อผู้ผ่านการคัดเลือกและมีสิทธิ์เข้าศึกษา วันที่ 28 เมษายน 2569
+-รายงานตัวขึ้นทะเบียนเป็นนักศึกษาและชำระเงิน ผ่านระบบบริการการศึกษา ESS วันที่ 29-30 เมษายน 2569
+-ยืนยันสิทธิ์ในระบบ TCAS วันที่ 2 - 3 พฤษภาคม 2569
+รอบ 4 Direct Admission (ยังไม่มีกำหนดการรับสมัคร)
+วันเปิดภาคเรียน (ภาคปกติ)
+วันที่ 22 มิถุนายน 2569</t>
+  </si>
 </sst>
 </file>
 
@@ -823,7 +821,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -833,9 +831,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1185,42 +1180,42 @@
     </row>
     <row r="2" spans="1:1" ht="13.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="4" t="s">
+    <row r="4" spans="1:1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="4" t="s">
+    <row r="6" spans="1:1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="4" t="s">
+    <row r="8" spans="1:1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="17.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="4" t="s">
+    <row r="9" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="4" t="s">
         <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="5" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.45">

--- a/workaw_data.xlsx
+++ b/workaw_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kuck\Documents\AI\demo\workaw_chatbot\workaw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{909B913C-0A6C-47A3-A2DC-EFB8F1CBA00B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8DF451-1F4C-4AD1-A502-3A174C5318C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13996" xr2:uid="{64D59F0A-8640-4EF3-95CC-009CBE3BA196}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>context</t>
   </si>
@@ -779,6 +779,65 @@
 วันเปิดภาคเรียน (ภาคปกติ)
 วันที่ 22 มิถุนายน 2569</t>
   </si>
+  <si>
+    <t>ข้อมูลทั่วไป
+คณะศึกษาศาสตร์และนวัตกรรมการศึกษา มหาวิทยาลัยกาฬสินธุ์ 
+Faculty of Education and Educational Innovation: Kalasin University
+ประวัติและความเป็นมา 
+พ.ศ. 2538 ได้เปิดสอนหลักสูตรครุศาสตรบัณฑิต ภายใต้ คณะศิลปศาสตร์และวิทยาศาสตร์ ของ โครงการจัดตั้งมหาวิทยาลัยราชภัฏกาฬสินธุ์ เพื่อผลิตบัณฑิตทางการศึกษาในสาขาวิชาชีพครู ตอบสนองความต้องการของท้องถิ่นและชุมชนในจังหวัดกาฬสินธุ์
+  	พ.ศ. 2547 ได้มีการจัดตั้งเป็น คณะครุศาสตร์ มหาวิทยาลัยราชภัฏกาฬสินธุ์ อย่างเป็นทางการ เพื่อมุ่งเน้นการพัฒนาครูมืออาชีพตามมาตรฐานของคุรุสภา และขยายหลักสูตรทางการศึกษาในระดับปริญญาตรีและบัณฑิตศึกษา
+  	พ.ศ. 2558 หลังการยกระดับเป็น มหาวิทยาลัยกาฬสินธุ์ ได้มีการ ปรับโครงสร้างจากคณะครุศาสตร์เป็น “คณะศึกษาศาสตร์และนวัตกรรมการศึกษา” ซึ่งเดิมคือ คณะครุศาสตร์ ซึ่งตั้งขึ้นตามมติสภามหาวิทยาลัยราชภัฏกาฬสินธุ์ เมื่อเดือนมิถุนายน พ.ศ. 2558 โดยมีพระราชบัญญัติจัดตั้งมหาวิทยาลัยกาฬสินธุ์ขึ้น และประกาศในราชกิจจานุเบกษา เล่ม 132 ตอนที่ 86ก เมื่อวันที่ 8 กันยายน 2558 โดยรวมสถาบันการศึกษาเดิมที่มีอยู่ในพื้นที่จังหวัดกาฬสินธุ์เข้าด้วยกัน ได้แก่ วิทยาลัยครูกาฬสินธุ์ และมหาวิทยาลัยเทคโนโลยีราชมงคลอีสาน วิทยาเขตกาฬสินธุ์ ตามมติของมหาวิทยาลัยเทคโนโลยีราชมงคลอีสาน จัดตั้งเป็นมหาวิทยาลัยกาฬสินธุ์เพื่อการบูรณาการทางวิชาการกับชุมชนและเป็นส่วนราชการภายใต้กระทรวงศึกษาธิการ ต่อมาในปี พ.ศ. 2561 ได้มีการปรับโครงสร้างของหน่วยงานภายในมหาวิทยาลัยกาฬสินธุ์ใหม่ พ.ศ. 2561 ตามประกาศของกระทรวงศึกษาธิการ เรื่อง การจัดตั้งส่วนราชการภายในมหาวิทยาลัยกาฬสินธุ์ กระทรวงศึกษาธิการ พ.ศ. 2561 ประกาศในราชกิจจานุเบกษา เล่ม 135 ตอนที่ 69 ง ลงวันที่ 13 กันยายน 2561 จึงเปลี่ยนชื่อเป็น คณะศึกษาศาสตร์และนวัตกรรมการศึกษา จนถึงปัจจุบัน
+สัญลักษณ์ประจำคณะ คือ ดอกกล้วยไม้
+สีประจำคณะ คือ สีม่วง
+วิสัยทัศน์ (Vision) คือ คณะศึกษาศาสตร์ชั้นนำด้านนวัตกรรมการเรียนรู้ เพื่อพัฒนาท้องถิ่นอย่างยั่งยืน (บรรลุในปี 2572)” ซึ่งสะท้อนความมุ่งมั่นที่จะเป็นผู้นำด้านนวัตกรรมบูรณาการเทคโนโลยีและการสอนสมัยใหม่เพื่อสร้างผลกระทบต่อชุมชนท้องถิ่น
+พันธกิจ (Mission) คือ 
+•	M1: ผลิตบัณฑิตครูคุณภาพสูงที่มีสมรรถนะวิชาชีพและการจัดการศึกษา
+•	M2: วิจัยและพัฒนานวัตกรรมการเรียนรู้เพื่อยกระดับคุณภาพการศึกษาท้องถิ่น
+•	M3: บริการวิชาการและถ่ายทอดองค์ความรู้เพื่อพัฒนาชุมชน และการศึกษาท้องถิ่นอย่างยั่งยืน
+ค่านิยมหลัก (Values) คือ GIVESA
+•	Growth Mindset 
+•	Innovation
+•	Valuing People
+•	Ethics and Transparency
+•	Societal Contributions
+•	Agility and Resilience
+วัฒนธรรม (Culture) คือ การทำงานแบบมีส่วนร่วม  
+บริบทและจุดเน้นของคณะ คือ
+•	ทิศทางองค์กร คณะดำเนินงานสอดคล้องกับทิศทางของมหาวิทยาลัยที่มุ่งสู่การเป็น “มหาวิทยาลัยเพื่อการพัฒนาท้องถิ่น อย่างยั่งยืนและยกระดับมาตรฐานสู่สากล”
+•	จุดเน้นหลัก นวัตกรรมการเรียนรู้ เพื่อการพัฒนาครูยุคดิจิทัล และการสร้างนวัตกรรมการศึกษาที่ตอบโจทย์สังคม
+•	สมรรถนะหลัก ความเชี่ยวชาญในการผลิตและพัฒนาครูนวัตกรเพื่อยกระดับคุณภาพการศึกษาเพื่อพัฒนาท้องถิ่นอย่างยั่งยืน
+คณบดีคนปัจจุบัน คือ ผศ.ดร.ลาวัณย์ ดุลยชาติ (คณบดี คนที่ 3) ดำรงตำแหน่งตั้งแต่วันที่ 14 กุมภาพันธ์ 2568
+จำนวนบุคลากรของคณะ จำนวน 67 คน ดังนี้
+•	สายวิชาการ จำนวน 50 คน
+•	สายสนับสนุน จำนวน 17 คน
+วิธีการสมัครเรียน
+สมัครผ่านระบบออนไลน์ https://admission.ksu.ac.th/ และดำเนินการตามขั้นตอนที่ระบุในเว็บไซต์
+อาคารสถานที่ คณะศึกษาศาสตร์และนวัตกรรมการศึกษา มีอาคารจำนวน 2 หลัง มีห้องเรียน 20 ห้อง ห้องปฏิบัติการ 3 ห้อง ห้องประชุม 2 ห้อง ห้อง Co-working Space ห้องสมุดดิจิทัล ดังนี้
+•	อาคารเรียนรวม
+•	อาคารศูนย์ความเป็นเลิศด้านการพัฒนาการเรียนรู้ตลอดชีวิตและพัฒนาทักษะเพื่ออนาคต
+รูปแบบการจัดการเรียนการสอน
+•	หลักสูตรครุศาสตรบัณฑิต สาขาวิชานวัตกรรมการจัดการเรียนรู้ จัดการเรียนการสอนในรูปแบบออนไซต์ ณ คณะศึกษาศาสตร์และนวัตกรรมการศึกษา มหาวิทยาลัยกาฬสินธุ์ (พื้นที่นามน)
+•	หลักสูตรประกาศนียบัตรบัณฑิต (ป.บัณฑิต วิชาชีพครู) สาขาวิชานวัตกรรมการจัดการเรียนรู้ จัดการเรียนการสอนในรูปแบบผสมผสาน ทั้งรูปแบบออนไลน์และออนไซต์
+•	หลักสูตรประกาศนียบัตรบัณฑิตชั้นสูง สาขาวิชานวัตกรรมการจัดการเรียนรู้ จัดการเรียนการสอนในรูปแบบผสมผสาน ทั้งรูปแบบออนไลน์และออนไซต์ (ออนไลน์ 90%)
+•	หลักสูตรครุศาสตรมหาบัณฑิต สาขาวิชาการบริหารการศึกษา จัดการเรียนการสอนในรูปแบบผสมผสาน ทั้งรูปแบบออนไลน์และออนไซต์
+•	หลักสูตรครุศาสตรมหาบัณฑิต สาขาวิชานวัตกรรมการจัดการเรียนรู้ จัดการเรียนการสอนในรูปแบบผสมผสาน ทั้งรูปแบบออนไลน์และออนไซต์ (ออนไลน์ 70%)
+•	หลักสูตรครุศาสตรดุษฎีบัณฑิต สาขาวิชานวัตกรรมการจัดการเรียนรู้ จัดการเรียนการสอนในรูปแบบผสมผสาน ทั้งรูปแบบออนไลน์และออนไซต์ (ออนไลน์ 70%)
+ระเบียบการแต่งกายของนักศึกษาระดับปริญญาตรี
+นักศึกษาชาย
+•	เสื้อเชิ้ตแขนสั้น หรือแขนยาว สีขาวไม่มีลวดลาย ปกเสื้อแบบปลายแหลม มีกระเป๋าติดทางอกด้านซ้าย
+•	กางเกงขายาวแบบสากล สุภาพ ผ้าสีดำไม่มีลวดลาย
+•	รองเท้าคัทชู สีดำแบบเรียบ ถุงเท้าสีดำ
+•	เนคไทสีฟ้าพยับหมอก เข็มกลัดเนคไท ตราสัญลักษณ์มหาวิทยาลัย
+•	เข็มขัดหนังสีดำ ขนาดกว้าง 3 ซม. หัวเข็มขัดโลหะเงิน สี่เหลี่ยมผืนผ้า ดุนเป็นรูปตราสัญลักษณ์มหาวิทยาลัย
+นักศึกษาหญิง
+•	เสื้อเชิ้ตแขนสั้น สีขาวไม่มีลวดลาย ปกเสื้อแบบปลายแหลม
+•	กระโปรงเอวสูง ทรงสอบ ผ้าสีดำไม่มีลวดลาย ความยาวคลุมหัวเข่า
+•	รองเท้าคัทชูสีดำแบบเรียบ
+•	กระดุมโลหะเงิน เส้นผ่านศูนย์กลาง 1.5 ซม. ดุนเป็นรูปตราสัญลักษณ์มหาวิทยาลัย
+•	เข็มกลัดเงิน เคลือบอะคริลิคสีฟ้า ตราสัญลักษณ์มหาวิทยาลัย
+•	เข็มขัดหนังสีดำ ขนาดกว้าง 3 ซม. หัวเข็มขัดโลหะเงิน สี่เหลี่ยมผืนผ้า ดุนเป็นรูปตราสัญลักษณ์มหาวิทยาลัย
+หมายเหตุ : สามารถซื้ออุปกรณ์เครื่องแต่งกายได้ที่ งานคลังมหาวิทยาลัยกาฬสินธุ์ ทั้ง 2 พื้นที่</t>
+  </si>
 </sst>
 </file>
 
@@ -1218,8 +1277,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A10" s="4"/>
+    <row r="10" spans="1:1" ht="409.5" x14ac:dyDescent="0.45">
+      <c r="A10" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A11" s="4"/>
